--- a/data/satisfaction_detail/2026/1-6月/参会人员.xlsx
+++ b/data/satisfaction_detail/2026/1-6月/参会人员.xlsx
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>9.51</v>
+        <v>9.52</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>9.94</v>
@@ -579,7 +579,7 @@
         <v>9.630000000000001</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>9.98</v>
+        <v>9.970000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -592,7 +592,7 @@
         <v>9.25</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>9.970000000000001</v>
+        <v>9.960000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -605,7 +605,7 @@
         <v>9.380000000000001</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>9.94</v>
+        <v>9.93</v>
       </c>
     </row>
     <row r="13">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>9.470000000000001</v>
+        <v>9.48</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>9.92</v>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>8.779999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>9.949999999999999</v>
@@ -657,7 +657,7 @@
         <v>9.890000000000001</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>9.94</v>
+        <v>9.949999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>9.93</v>
+        <v>9.94</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>9.98</v>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.81</v>
       </c>
       <c r="C18" s="3" t="n">
         <v>10</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>9.83</v>
+        <v>9.85</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>10</v>
